--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
@@ -139,12 +139,6 @@
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11402</t>
   </si>
   <si>
@@ -163,12 +157,6 @@
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -811,6 +799,12 @@
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">13122</t>
   </si>
   <si>
@@ -1348,6 +1342,12 @@
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4203</t>
   </si>
   <si>
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:23</t>
+    <t xml:space="preserve">2026-09-09 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2965,7 +2965,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>85.6</v>
+        <v>84.17</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2997,7 +2997,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>84.17</v>
+        <v>82.35</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -3029,7 +3029,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>82.35</v>
+        <v>82.05</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3061,7 +3061,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>82.05</v>
+        <v>81.57</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3072,10 +3072,10 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>48</v>
@@ -3093,7 +3093,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>81.75</v>
+        <v>80</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3104,28 +3104,28 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>81.57</v>
+        <v>93.02</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3136,28 +3136,28 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>80</v>
+        <v>92.98</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3168,28 +3168,28 @@
         <v>2022</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>93.02</v>
+        <v>92.75</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3200,28 +3200,28 @@
         <v>2022</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>92.98</v>
+        <v>92.68</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3232,28 +3232,28 @@
         <v>2022</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>92.75</v>
+        <v>92.66</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3264,28 +3264,28 @@
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>92.68</v>
+        <v>92.63</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3296,28 +3296,28 @@
         <v>2022</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>92.66</v>
+        <v>92.44</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3331,7 +3331,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3340,16 +3340,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>92.63</v>
+        <v>92.05</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3360,10 +3360,10 @@
         <v>2022</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3372,16 +3372,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>92.44</v>
+        <v>92.05</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3392,10 +3392,10 @@
         <v>2022</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3404,16 +3404,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>92.05</v>
+        <v>92.03</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3424,10 +3424,10 @@
         <v>2022</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3436,16 +3436,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>92.05</v>
+        <v>91.76</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3459,7 +3459,7 @@
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3468,16 +3468,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>92.03</v>
+        <v>91.7</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3488,10 +3488,10 @@
         <v>2022</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3500,16 +3500,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>91.76</v>
+        <v>91.25</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3520,10 +3520,10 @@
         <v>2022</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3532,16 +3532,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>91.7</v>
+        <v>91.13</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3555,7 +3555,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3564,16 +3564,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>91.25</v>
+        <v>90.88</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3584,10 +3584,10 @@
         <v>2022</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3596,16 +3596,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>91.13</v>
+        <v>90.86</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3616,10 +3616,10 @@
         <v>2022</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3628,16 +3628,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>90.88</v>
+        <v>90.82</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3648,10 +3648,10 @@
         <v>2022</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3660,16 +3660,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>90.86</v>
+        <v>90.7</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3680,10 +3680,10 @@
         <v>2022</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3692,16 +3692,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>90.82</v>
+        <v>90.62</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3712,10 +3712,10 @@
         <v>2022</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3724,16 +3724,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>90.7</v>
+        <v>90.58</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3744,10 +3744,10 @@
         <v>2022</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3756,16 +3756,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>90.62</v>
+        <v>90.54</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3776,10 +3776,10 @@
         <v>2022</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3788,16 +3788,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90.58</v>
+        <v>90.45</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3808,10 +3808,10 @@
         <v>2022</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3820,16 +3820,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>90.54</v>
+        <v>90.38</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3843,7 +3843,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3852,16 +3852,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>90.45</v>
+        <v>90.32</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3872,10 +3872,10 @@
         <v>2022</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3884,16 +3884,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>90.38</v>
+        <v>90.27</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3904,28 +3904,28 @@
         <v>2022</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>90.32</v>
+        <v>90.17</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3936,28 +3936,28 @@
         <v>2022</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>90.27</v>
+        <v>90.14</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3968,10 +3968,10 @@
         <v>2022</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -3980,16 +3980,16 @@
         <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>90.17</v>
+        <v>90.11</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -4003,7 +4003,7 @@
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>113</v>
@@ -4012,16 +4012,16 @@
         <v>114</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>90.14</v>
+        <v>90.08</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4035,7 +4035,7 @@
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>115</v>
@@ -4044,16 +4044,16 @@
         <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>90.11</v>
+        <v>90.08</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4064,10 +4064,10 @@
         <v>2022</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>117</v>
@@ -4076,16 +4076,16 @@
         <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>90.08</v>
+        <v>90.04</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4096,10 +4096,10 @@
         <v>2022</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>119</v>
@@ -4108,16 +4108,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>90.08</v>
+        <v>90.01</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4128,10 +4128,10 @@
         <v>2022</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -4140,16 +4140,16 @@
         <v>122</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>90.04</v>
+        <v>90</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4160,10 +4160,10 @@
         <v>2022</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>123</v>
@@ -4172,16 +4172,16 @@
         <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>90.01</v>
+        <v>89.98</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4192,10 +4192,10 @@
         <v>2022</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>125</v>
@@ -4204,16 +4204,16 @@
         <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>90</v>
+        <v>89.93</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4224,10 +4224,10 @@
         <v>2022</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>127</v>
@@ -4236,16 +4236,16 @@
         <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>89.98</v>
+        <v>89.93</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4256,10 +4256,10 @@
         <v>2022</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>129</v>
@@ -4268,16 +4268,16 @@
         <v>130</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>89.93</v>
+        <v>89.92</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4288,10 +4288,10 @@
         <v>2022</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>131</v>
@@ -4300,16 +4300,16 @@
         <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>89.93</v>
+        <v>89.91</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4323,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>133</v>
@@ -4332,16 +4332,16 @@
         <v>134</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>89.92</v>
+        <v>89.9</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4355,7 +4355,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>135</v>
@@ -4364,16 +4364,16 @@
         <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>89.91</v>
+        <v>89.77</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4384,10 +4384,10 @@
         <v>2022</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>137</v>
@@ -4396,16 +4396,16 @@
         <v>138</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>89.9</v>
+        <v>89.75</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4416,10 +4416,10 @@
         <v>2022</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>139</v>
@@ -4428,16 +4428,16 @@
         <v>140</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>89.77</v>
+        <v>89.66</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4448,10 +4448,10 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
@@ -4460,16 +4460,16 @@
         <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>89.75</v>
+        <v>89.61</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4480,10 +4480,10 @@
         <v>2022</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>143</v>
@@ -4492,16 +4492,16 @@
         <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>89.66</v>
+        <v>89.58</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4512,10 +4512,10 @@
         <v>2022</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>145</v>
@@ -4524,16 +4524,16 @@
         <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>89.61</v>
+        <v>89.51</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4544,10 +4544,10 @@
         <v>2022</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>147</v>
@@ -4556,16 +4556,16 @@
         <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>89.58</v>
+        <v>89.44</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4576,10 +4576,10 @@
         <v>2022</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>149</v>
@@ -4588,16 +4588,16 @@
         <v>150</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>89.51</v>
+        <v>89.42</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4608,28 +4608,28 @@
         <v>2022</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>89.44</v>
+        <v>89.36</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4640,28 +4640,28 @@
         <v>2022</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>89.42</v>
+        <v>89.31</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4675,25 +4675,25 @@
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>89.36</v>
+        <v>89.26</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4704,10 +4704,10 @@
         <v>2022</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4716,16 +4716,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>89.31</v>
+        <v>89.23</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4736,10 +4736,10 @@
         <v>2022</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4748,16 +4748,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>89.26</v>
+        <v>89.21</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4768,10 +4768,10 @@
         <v>2022</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4780,16 +4780,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>89.23</v>
+        <v>89.2</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4800,10 +4800,10 @@
         <v>2022</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4812,16 +4812,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>89.21</v>
+        <v>89.01</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4832,10 +4832,10 @@
         <v>2022</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4844,16 +4844,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>89.2</v>
+        <v>89.01</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4867,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4876,16 +4876,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>89.01</v>
+        <v>89</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4896,10 +4896,10 @@
         <v>2022</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4908,16 +4908,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>89.01</v>
+        <v>88.93</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4928,10 +4928,10 @@
         <v>2022</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4940,16 +4940,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>89</v>
+        <v>88.92</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4960,10 +4960,10 @@
         <v>2022</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4972,16 +4972,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>88.93</v>
+        <v>88.91</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -4992,10 +4992,10 @@
         <v>2022</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -5004,16 +5004,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>88.92</v>
+        <v>88.8</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -5024,10 +5024,10 @@
         <v>2022</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -5036,16 +5036,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>88.91</v>
+        <v>88.78</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5056,10 +5056,10 @@
         <v>2022</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5068,16 +5068,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>88.8</v>
+        <v>88.77</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5088,10 +5088,10 @@
         <v>2022</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5100,16 +5100,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>88.78</v>
+        <v>88.76</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5120,10 +5120,10 @@
         <v>2022</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5132,16 +5132,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>88.77</v>
+        <v>88.66</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5152,10 +5152,10 @@
         <v>2022</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5164,16 +5164,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>88.76</v>
+        <v>88.66</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5184,10 +5184,10 @@
         <v>2022</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5196,16 +5196,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>88.66</v>
+        <v>88.65</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5219,7 +5219,7 @@
         <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5228,16 +5228,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>88.66</v>
+        <v>88.65</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5251,7 +5251,7 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5260,16 +5260,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>88.65</v>
+        <v>88.43</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5280,10 +5280,10 @@
         <v>2022</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5292,16 +5292,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>88.65</v>
+        <v>88.39</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5312,10 +5312,10 @@
         <v>2022</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5324,16 +5324,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>88.43</v>
+        <v>88.37</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5344,10 +5344,10 @@
         <v>2022</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5356,16 +5356,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>88.39</v>
+        <v>88.3</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5376,10 +5376,10 @@
         <v>2022</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5388,16 +5388,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>88.37</v>
+        <v>88.3</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5408,10 +5408,10 @@
         <v>2022</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5420,16 +5420,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>88.3</v>
+        <v>88.26</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5443,7 +5443,7 @@
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5452,16 +5452,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>88.3</v>
+        <v>88.23</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5472,10 +5472,10 @@
         <v>2022</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5484,16 +5484,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>88.26</v>
+        <v>88.23</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5504,10 +5504,10 @@
         <v>2022</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5516,16 +5516,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>88.23</v>
+        <v>88.22</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5536,10 +5536,10 @@
         <v>2022</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5548,16 +5548,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>88.23</v>
+        <v>88.19</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5571,7 +5571,7 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5580,16 +5580,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>88.22</v>
+        <v>88.17</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5600,10 +5600,10 @@
         <v>2022</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5612,16 +5612,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>88.19</v>
+        <v>88.14</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5632,10 +5632,10 @@
         <v>2022</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5644,16 +5644,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>88.17</v>
+        <v>88.11</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5667,7 +5667,7 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5676,16 +5676,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>88.14</v>
+        <v>88.07</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5699,7 +5699,7 @@
         <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5708,16 +5708,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>88.11</v>
+        <v>87.95</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5728,10 +5728,10 @@
         <v>2022</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5740,16 +5740,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>88.07</v>
+        <v>87.93</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5760,10 +5760,10 @@
         <v>2022</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5772,16 +5772,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>87.95</v>
+        <v>87.78</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5795,7 +5795,7 @@
         <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5804,16 +5804,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>87.93</v>
+        <v>87.7</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5827,7 +5827,7 @@
         <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5836,16 +5836,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>87.78</v>
+        <v>87.69</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5856,10 +5856,10 @@
         <v>2022</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5868,16 +5868,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>87.7</v>
+        <v>87.66</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5888,10 +5888,10 @@
         <v>2022</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5900,16 +5900,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>87.69</v>
+        <v>87.64</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5920,10 +5920,10 @@
         <v>2022</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5932,16 +5932,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>87.66</v>
+        <v>87.6</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5952,10 +5952,10 @@
         <v>2022</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5964,16 +5964,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>87.64</v>
+        <v>87.41</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5984,10 +5984,10 @@
         <v>2022</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5996,16 +5996,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>87.6</v>
+        <v>87.37</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -6019,7 +6019,7 @@
         <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6028,16 +6028,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>87.41</v>
+        <v>87.17</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6048,10 +6048,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6060,16 +6060,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>87.37</v>
+        <v>87.16</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6080,10 +6080,10 @@
         <v>2022</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6092,16 +6092,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>87.17</v>
+        <v>87.15</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6112,10 +6112,10 @@
         <v>2022</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6124,16 +6124,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>87.16</v>
+        <v>87.11</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6144,10 +6144,10 @@
         <v>2022</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6156,16 +6156,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>87.15</v>
+        <v>87.05</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6179,7 +6179,7 @@
         <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6188,16 +6188,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>87.11</v>
+        <v>87.05</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6208,10 +6208,10 @@
         <v>2022</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6220,16 +6220,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>87.05</v>
+        <v>87.03</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6240,10 +6240,10 @@
         <v>2022</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6252,16 +6252,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>87.05</v>
+        <v>87.02</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6272,10 +6272,10 @@
         <v>2022</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6284,16 +6284,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>87.03</v>
+        <v>87.02</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6307,7 +6307,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6316,16 +6316,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>87.02</v>
+        <v>86.99</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6336,10 +6336,10 @@
         <v>2022</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6348,16 +6348,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>87.02</v>
+        <v>86.91</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6368,10 +6368,10 @@
         <v>2022</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6380,16 +6380,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>86.99</v>
+        <v>86.91</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6400,10 +6400,10 @@
         <v>2022</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6412,16 +6412,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>86.91</v>
+        <v>86.86</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6432,10 +6432,10 @@
         <v>2022</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6444,16 +6444,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>86.86</v>
+        <v>86.84</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6464,10 +6464,10 @@
         <v>2022</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6476,16 +6476,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>86.84</v>
+        <v>86.82</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6496,10 +6496,10 @@
         <v>2022</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6508,16 +6508,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>86.82</v>
+        <v>86.67</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6528,10 +6528,10 @@
         <v>2022</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6540,10 +6540,10 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6560,10 +6560,10 @@
         <v>2022</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6572,16 +6572,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>86.67</v>
+        <v>86.64</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6592,10 +6592,10 @@
         <v>2022</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6604,10 +6604,10 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6624,10 +6624,10 @@
         <v>2022</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6636,16 +6636,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>86.64</v>
+        <v>86.62</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6656,10 +6656,10 @@
         <v>2022</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6668,10 +6668,10 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6688,10 +6688,10 @@
         <v>2022</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6700,16 +6700,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>86.62</v>
+        <v>86.61</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6720,10 +6720,10 @@
         <v>2022</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6732,16 +6732,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>86.61</v>
+        <v>86.55</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6752,10 +6752,10 @@
         <v>2022</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6764,16 +6764,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>86.55</v>
+        <v>86.54</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6784,10 +6784,10 @@
         <v>2022</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6796,16 +6796,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>86.54</v>
+        <v>86.52</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6816,10 +6816,10 @@
         <v>2022</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6828,16 +6828,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>86.52</v>
+        <v>86.51</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6851,7 +6851,7 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6860,16 +6860,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>86.51</v>
+        <v>86.45</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6880,10 +6880,10 @@
         <v>2022</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6892,16 +6892,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>86.45</v>
+        <v>86.37</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6912,10 +6912,10 @@
         <v>2022</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6924,16 +6924,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>86.37</v>
+        <v>86.36</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6944,10 +6944,10 @@
         <v>2022</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6956,16 +6956,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>86.36</v>
+        <v>86.34</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6976,10 +6976,10 @@
         <v>2022</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -6988,16 +6988,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>86.34</v>
+        <v>86.23</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -7008,10 +7008,10 @@
         <v>2022</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7020,16 +7020,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>86.23</v>
+        <v>86.22</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7040,10 +7040,10 @@
         <v>2022</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7052,16 +7052,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>86.22</v>
+        <v>86.14</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7075,7 +7075,7 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7084,16 +7084,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>86.14</v>
+        <v>86.13</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7107,7 +7107,7 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7116,16 +7116,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>86.13</v>
+        <v>85.91</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7136,10 +7136,10 @@
         <v>2022</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7148,16 +7148,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>85.91</v>
+        <v>85.84</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7168,10 +7168,10 @@
         <v>2022</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7180,16 +7180,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>85.84</v>
+        <v>85.8</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7200,10 +7200,10 @@
         <v>2022</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7212,16 +7212,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>85.8</v>
+        <v>85.79</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7232,10 +7232,10 @@
         <v>2022</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7244,16 +7244,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>85.79</v>
+        <v>85.75</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7264,10 +7264,10 @@
         <v>2022</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7276,10 +7276,10 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7296,10 +7296,10 @@
         <v>2022</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7308,16 +7308,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>85.75</v>
+        <v>85.72</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7328,10 +7328,10 @@
         <v>2022</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7340,16 +7340,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>85.72</v>
+        <v>85.64</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7360,10 +7360,10 @@
         <v>2022</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7372,16 +7372,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>85.64</v>
+        <v>85.62</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7392,10 +7392,10 @@
         <v>2022</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7404,16 +7404,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>85.62</v>
+        <v>85.58</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7424,10 +7424,10 @@
         <v>2022</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7436,10 +7436,10 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7459,7 +7459,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7468,16 +7468,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>85.58</v>
+        <v>85.51</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7488,10 +7488,10 @@
         <v>2022</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7500,16 +7500,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>85.51</v>
+        <v>85.32</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7520,10 +7520,10 @@
         <v>2022</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7532,16 +7532,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>85.32</v>
+        <v>85.26</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7552,10 +7552,10 @@
         <v>2022</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7564,16 +7564,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>85.26</v>
+        <v>85.21</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7584,10 +7584,10 @@
         <v>2022</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7596,16 +7596,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>85.21</v>
+        <v>85.11</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7619,7 +7619,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7628,16 +7628,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>85.11</v>
+        <v>85.07</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7648,10 +7648,10 @@
         <v>2022</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7660,16 +7660,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>85.07</v>
+        <v>84.96</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7680,10 +7680,10 @@
         <v>2022</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7692,16 +7692,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>84.96</v>
+        <v>84.94</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7712,10 +7712,10 @@
         <v>2022</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7724,16 +7724,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>84.94</v>
+        <v>84.93</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7744,10 +7744,10 @@
         <v>2022</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7756,16 +7756,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>84.93</v>
+        <v>84.85</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7776,10 +7776,10 @@
         <v>2022</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7788,16 +7788,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>84.85</v>
+        <v>84.8</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7808,10 +7808,10 @@
         <v>2022</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7820,16 +7820,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>84.8</v>
+        <v>84.64</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7840,10 +7840,10 @@
         <v>2022</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7852,16 +7852,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>84.64</v>
+        <v>84.62</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7872,10 +7872,10 @@
         <v>2022</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7884,16 +7884,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>84.62</v>
+        <v>84.5</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7904,10 +7904,10 @@
         <v>2022</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7916,16 +7916,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>84.5</v>
+        <v>84.46</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7936,10 +7936,10 @@
         <v>2022</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7948,16 +7948,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>84.46</v>
+        <v>84.34</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7971,7 +7971,7 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -7980,16 +7980,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>84.34</v>
+        <v>84.13</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -8003,7 +8003,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -8012,16 +8012,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>84.13</v>
+        <v>83.81</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8035,7 +8035,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8044,16 +8044,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>83.81</v>
+        <v>83.29</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8067,7 +8067,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8076,16 +8076,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>83.29</v>
+        <v>83.18</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8099,7 +8099,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8108,16 +8108,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>83.18</v>
+        <v>82.87</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8128,10 +8128,10 @@
         <v>2022</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8140,16 +8140,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>82.87</v>
+        <v>82.4</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8163,7 +8163,7 @@
         <v>5</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8172,16 +8172,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>82.4</v>
+        <v>81.52</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8195,7 +8195,7 @@
         <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8204,16 +8204,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>81.52</v>
+        <v>81.27</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8224,10 +8224,10 @@
         <v>2022</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8236,16 +8236,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>81.27</v>
+        <v>81.16</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8259,7 +8259,7 @@
         <v>6</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8268,16 +8268,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>81.16</v>
+        <v>80.43</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8288,10 +8288,10 @@
         <v>2022</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>380</v>
@@ -8300,16 +8300,16 @@
         <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>80.43</v>
+        <v>80.23</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8320,10 +8320,10 @@
         <v>2022</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>382</v>
@@ -8332,16 +8332,16 @@
         <v>383</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>80.23</v>
+        <v>79.73</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8352,10 +8352,10 @@
         <v>2022</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>384</v>
@@ -8364,16 +8364,16 @@
         <v>385</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>79.73</v>
+        <v>79.06</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8387,7 +8387,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>386</v>
@@ -8396,16 +8396,16 @@
         <v>387</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>79.06</v>
+        <v>76.26</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8416,28 +8416,28 @@
         <v>2022</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>110</v>
+        <v>388</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>57</v>
+        <v>391</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>58</v>
+        <v>392</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>76.26</v>
+        <v>94.67</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8448,28 +8448,28 @@
         <v>2022</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D186" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="G186" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F186" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>94.67</v>
+        <v>92.24</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8483,7 +8483,7 @@
         <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>396</v>
@@ -8492,16 +8492,16 @@
         <v>397</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>92.24</v>
+        <v>92.2</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8512,28 +8512,28 @@
         <v>2022</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>92.2</v>
+        <v>91.24</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8544,10 +8544,10 @@
         <v>2022</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>401</v>
@@ -8556,16 +8556,16 @@
         <v>402</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>91.24</v>
+        <v>90.97</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8576,10 +8576,10 @@
         <v>2022</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>403</v>
@@ -8588,16 +8588,16 @@
         <v>404</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>90.97</v>
+        <v>90.91</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8608,22 +8608,22 @@
         <v>2022</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8640,10 +8640,10 @@
         <v>2022</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>408</v>
@@ -8652,16 +8652,16 @@
         <v>409</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>90.91</v>
+        <v>90.84</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8672,10 +8672,10 @@
         <v>2022</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>410</v>
@@ -8684,16 +8684,16 @@
         <v>411</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>90.84</v>
+        <v>90.51</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8704,10 +8704,10 @@
         <v>2022</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>412</v>
@@ -8716,16 +8716,16 @@
         <v>413</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>90.51</v>
+        <v>90.36</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8739,7 +8739,7 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>414</v>
@@ -8748,16 +8748,16 @@
         <v>415</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>90.36</v>
+        <v>89.96</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8771,7 +8771,7 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>416</v>
@@ -8780,16 +8780,16 @@
         <v>417</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>89.96</v>
+        <v>89.86</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8800,10 +8800,10 @@
         <v>2022</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>418</v>
@@ -8812,16 +8812,16 @@
         <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>89.86</v>
+        <v>89.52</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8832,10 +8832,10 @@
         <v>2022</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8844,16 +8844,16 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>89.52</v>
+        <v>89.38</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8867,7 +8867,7 @@
         <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
@@ -8876,16 +8876,16 @@
         <v>423</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>89.38</v>
+        <v>89.29</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8899,7 +8899,7 @@
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>424</v>
@@ -8908,16 +8908,16 @@
         <v>425</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>89.29</v>
+        <v>89.15</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8931,7 +8931,7 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>426</v>
@@ -8940,16 +8940,16 @@
         <v>427</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>89.15</v>
+        <v>89.12</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8963,7 +8963,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>428</v>
@@ -8972,16 +8972,16 @@
         <v>429</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>89.12</v>
+        <v>88.98</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -8992,10 +8992,10 @@
         <v>2022</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>430</v>
@@ -9004,16 +9004,16 @@
         <v>431</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>88.98</v>
+        <v>88.85</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -9024,10 +9024,10 @@
         <v>2022</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>432</v>
@@ -9036,16 +9036,16 @@
         <v>433</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>88.85</v>
+        <v>88.84</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9056,28 +9056,28 @@
         <v>2022</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>88.84</v>
+        <v>87.88</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9088,10 +9088,10 @@
         <v>2022</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>437</v>
@@ -9100,16 +9100,16 @@
         <v>438</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>87.88</v>
+        <v>87.85</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9120,10 +9120,10 @@
         <v>2022</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>439</v>
@@ -9132,16 +9132,16 @@
         <v>440</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>87.85</v>
+        <v>87.84</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9152,10 +9152,10 @@
         <v>2022</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>441</v>
@@ -9164,16 +9164,16 @@
         <v>442</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>87.84</v>
+        <v>87.64</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9187,7 +9187,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>443</v>
@@ -9196,10 +9196,10 @@
         <v>444</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9219,7 +9219,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>445</v>
@@ -9228,10 +9228,10 @@
         <v>446</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9251,7 +9251,7 @@
         <v>15</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>447</v>
@@ -9260,10 +9260,10 @@
         <v>448</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9283,7 +9283,7 @@
         <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>449</v>
@@ -9292,10 +9292,10 @@
         <v>450</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9315,7 +9315,7 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>451</v>
@@ -9324,10 +9324,10 @@
         <v>452</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9347,19 +9347,19 @@
         <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>453</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9379,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>454</v>
@@ -9388,10 +9388,10 @@
         <v>455</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9411,7 +9411,7 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>456</v>
@@ -9420,10 +9420,10 @@
         <v>457</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9443,7 +9443,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>458</v>
@@ -9452,10 +9452,10 @@
         <v>459</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9475,19 +9475,19 @@
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>460</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9507,7 +9507,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>461</v>
@@ -9516,10 +9516,10 @@
         <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9539,7 +9539,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>463</v>
@@ -9548,10 +9548,10 @@
         <v>464</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9571,7 +9571,7 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>465</v>
@@ -9580,10 +9580,10 @@
         <v>466</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9603,7 +9603,7 @@
         <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>467</v>
@@ -9612,10 +9612,10 @@
         <v>468</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9635,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>469</v>
@@ -9644,10 +9644,10 @@
         <v>470</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9667,7 +9667,7 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>471</v>
@@ -9676,10 +9676,10 @@
         <v>472</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9699,7 +9699,7 @@
         <v>2</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>473</v>
@@ -9708,10 +9708,10 @@
         <v>474</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:12</t>
+    <t xml:space="preserve">2026-09-18 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:32</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
